--- a/erp-server/erp-server-file/src/main/resources/excel/oms/PackagePlan.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/PackagePlan.xlsx
@@ -760,15 +760,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1306,100 +1309,101 @@
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="10.875" customWidth="1"/>
-    <col min="4" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="17" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
-    <col min="12" max="12" width="12.25" customWidth="1"/>
-    <col min="13" max="13" width="11.125" customWidth="1"/>
+    <col min="1" max="2" width="20" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.875" style="1" customWidth="1"/>
+    <col min="4" max="9" width="20" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17" style="1" customWidth="1"/>
+    <col min="11" max="11" width="20" style="1" customWidth="1"/>
+    <col min="12" max="12" width="12.25" style="1" customWidth="1"/>
+    <col min="13" max="13" width="11.125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" spans="1:14">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>27</v>
       </c>
     </row>
